--- a/03_coding/codebook.xlsx
+++ b/03_coding/codebook.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Codebook" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Categories" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimensions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage_scale_v1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,21 +29,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,10 +51,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,16 +424,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="52.2" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="47.7" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,14 +444,14 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>code_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>definition</t>
@@ -462,166 +459,1173 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>example_application</t>
+          <t>grounding_origin</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>origin_type</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>date_added</t>
+          <t>n_cells_v1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>COD-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>cross_provider_iam</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Identity &amp; Access Management</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TEMPLATE definition: mechanisms for federating identity/access across cloud providers.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EXAMPLE: study proposes a federated IAM broker across AWS/Azure/GCP.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TEMPLATE Coder</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Single-cloud / architecture-agnostic</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Segment treats one cloud only, or is written provider-agnostically with no cross-provider content.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (SP 800-145)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>COD-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>policy_enforcement</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Policy &amp; Compliance</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TEMPLATE definition: technical or organizational mechanisms enforcing governance policy across clouds.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EXAMPLE: study describes a policy-as-code engine evaluated on two providers.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TEMPLATE Coder</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D1.2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid-cloud</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Segment addresses cloud + on-premises (hybrid) as the stated architecture.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (SP 800-145)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>COD-03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>audit_traceability</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Monitoring &amp; Audit</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TEMPLATE definition: capability to produce unified audit trails spanning multiple cloud providers.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>EXAMPLE: study evaluates log aggregation across heterogeneous cloud audit APIs.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TEMPLATE Coder</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Multi-cloud - conceptual / review scope</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Multi-cloud is the review/survey scope or is acknowledged conceptually, without operating 2+ providers.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Abductive extension (Ali et al., 2025)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Abductive</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>COD-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>governance_gap</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Gap / Limitation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TEMPLATE definition: an explicitly identified shortcoming or open problem in current governance approaches.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>EXAMPLE: authors note no vendor-neutral standard exists for cross-cloud compliance reporting.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>TEMPLATE Coder</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D1.4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Multi-cloud - operational (2+ concurrent providers)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Segment implements, benchmarks or evaluates 2+ concurrent public providers (e.g. Azure Arc + AWS EKS + GCP Anthos).</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Abductive extension (Yeboah-Ofori et al., 2024)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Abductive</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D2.OC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>GV.OC Organizational Context</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Governance framed via organisational context/objectives.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF GV.OC)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D2.RM</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GV.RM Risk Mgmt Strategy</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Governance expressed as a risk-management strategy.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF GV.RM)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>D2.RR</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>GV.RR Roles, Responsibilities &amp; Authorities</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Governance via defined roles/responsibilities/authorities.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF GV.RR)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D2.PO</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>GV.PO Policy (policy instrument)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Governance via a defined security policy instrument / policy structure.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF GV.PO)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D2.OV</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GV.OV Oversight</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Governance via oversight / continuous evaluation.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF GV.OV)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>D2.SC</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>GV.SC Supply-Chain / Provider Relationships</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Governance of provider/supply-chain relationships.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF GV.SC)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Holistic / whole-framework governance (ISMS-level)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>A whole governance framework or management-system structure (ISO 27001 clauses; the entire GOVERN function; a complete ISG framework).</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Abductive extension (ISO/IEC 27001 ISMS)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Abductive</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Governance referenced / challenge documented, no framework</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Governance mentioned, or named as a challenge, without any framework or instrument being defined.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Abductive extension (this corpus)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Abductive</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Preventive control - access control, encryption, ABAC/RBAC</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>A preventive enforcement control is named: access control, encryption, RBAC/ABAC, configuration control (Annex A control-type: preventive).</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (ISO 27001 Annex A)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>D3.2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Detective control - monitoring, logging, audit</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>A detective enforcement control is named: monitoring, logging, intrusion detection, audit (Annex A control-type: detective).</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (ISO 27001 Annex A)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>D3.3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Corrective control - remediation, response</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>A corrective enforcement control is named: remediation or incident response (Annex A control-type: corrective).</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (ISO 27001 Annex A)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Policy specification only (no enforcement mechanism)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Policy is stated, required, or its challenge argued, but no concrete enforcement mechanism is defined.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Abductive extension (this corpus)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Abductive</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>D4.1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Provider-managed</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Control/obligation allocated to the provider.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (SSRM)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>D4.2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Customer-managed</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Control/obligation allocated to the customer.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (SSRM)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Shared / jointly-managed (SSRM across IaaS/PaaS/SaaS)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Responsibility split defined across provider and customer (per service model).</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (SSRM)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>D4.4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Boundary referenced, not allocated</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Shared responsibility mentioned, but no boundary actually allocated.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Abductive extension (this corpus)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Abductive</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ID - Risk identification / assessment</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Risk identification or assessment activity (incl. quantitative evaluation).</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF ID)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>D5.PR</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>PR - Protective safeguards</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Protective safeguards for posture.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF PR)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>DE - Continuous monitoring / detection (CSPM)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Continuous monitoring / detection, incl. CSPM tooling.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF DE)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>D5.RS</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>RS/RC - Response &amp; recovery</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Response and recovery activity.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (NIST CSF RS/RC)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>D5.X</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Risk referenced, no posture mechanism</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Risk mentioned but no posture-management mechanism given.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Abductive extension (this corpus)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Abductive</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Authentication &amp; Authorization</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Authentication and authorization mechanisms (topic 1).</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (Cuzzocrea topic 1)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>D6.IV</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Identity Verification &amp; Risk Mgmt</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Identity verification and risk management (topic 2).</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (Cuzzocrea topic 2)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>D6.AM</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Attribute Management</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Attribute management (topic 3).</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (Cuzzocrea topic 3)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>D6.SP</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Security and privacy of identity data (topic 4).</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (Cuzzocrea topic 4)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>D6.AC</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Audit &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Identity audit and compliance (topic 5).</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (Cuzzocrea topic 5)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>D6.UL</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>User Lifecycle Management</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Provisioning / deprovisioning / lifecycle synchronisation (topic 6).</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (Cuzzocrea topic 6)</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Federation</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Cross-provider interoperability and identity federation - SAML/OIDC/SSO, IdP-RP trust (topic 7).</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Deductive (Cuzzocrea topic 7)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Deductive</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Dimension not substantively addressed by this source</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Structural option: the source contains no segment addressing the dimension (coverage = No). Not a content code.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Structural option (coverage = No); not a content code</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -635,70 +1639,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26.1" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>grounding</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>assignment_rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Multi-Cloud Environment Focus</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Grounding: NIST SP 800-145 cloud deployment models (Mell &amp; Grance, 2011 - thesis Ch. 2); multi-cloud split per Ali et al. (2025) multi/hybrid distinction and Yeboah-Ofori et al. (2024) operational labs</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Assign the most specific architecture the segment actually addresses: operational multi-cloud (D1.4) &gt; conceptual multi-cloud (D1.3) &gt; hybrid (D1.2) &gt; single/agnostic (D1.1). Exactly one code per segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Governance</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Grounding: NIST CSF 2.0 GOVERN-function subcategories (NIST, 2024); ISMS clause structure per ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>If the segment names a specific governance instrument, use the matching GV code (D2.OC/RM/RR/PO/OV/SC). If it presents a whole management system / framework, use D2.FW. If governance is referenced or posed as a challenge without a structure, use D2.X. Exactly one code per segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Policy Enforcement</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Grounding: ISO/IEC 27001:2022 Annex A control-type attribute - preventive / detective / corrective (ISO/IEC, 2022); access-control mechanisms per NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>If a concrete enforcement mechanism is named, code its control type per the ISO/IEC 27001:2022 Annex A attribute (D3.1 preventive / D3.2 detective / D3.3 corrective - choose the dominant type). If policy is only specified or its need argued, use D3.4. Exactly one code per segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Shared Responsibility</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Grounding: CSA Security Guidance v5 Shared Security Responsibility Model - SSRM (CSA, 2021); NSA shared-responsibility guidance (2024)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Code by the allocation the segment makes: provider (D4.1), customer (D4.2), or jointly defined split (D4.3). If responsibility is referenced without allocating a boundary, use D4.4. Exactly one code per segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Risk Posture Management</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Grounding: NIST CSF 2.0 operational functions ID / PR / DE / RS-RC (NIST, 2024); CSPM per CSA Security Guidance v5 Domain 6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Code the CSF function of the posture activity the segment describes (D5.ID / D5.PR / D5.DE / D5.RS). If risk is referenced without a posture mechanism, use D5.X. Exactly one code per segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>IAM Federation</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Grounding: Cuzzocrea &amp; Belmerabet (2024) seven-topic IAM taxonomy; IdP-RP federation terminology per CSA Security Guidance v5 Domain 5 and Poehn &amp; Hillmann (2021) FIM reference model</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Code the IAM topic the segment addresses using the Cuzzocrea taxonomy (one topic per segment). Cross-provider interoperability and identity federation (SAML/OIDC/SSO, IdP-RP trust) = D6.IF. Exactly one code per segment.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>level</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>meaning (as published, ETECOM 2026 Sec. III-C)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Identity &amp; Access Management</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TEMPLATE - codes related to authN/authZ across cloud providers.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Substantive coverage of the dimension at organisational level</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Policy &amp; Compliance</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TEMPLATE - codes related to policy definition and enforcement mechanisms.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Limited, indirect, or advisory coverage</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Monitoring &amp; Audit</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TEMPLATE - codes related to observability, logging, and audit trails.</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No substantive treatment</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Gap / Limitation</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TEMPLATE - codes capturing explicitly stated research/practice gaps.</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No level implies explicit cross-provider coordination; D1 measures explicit multi-cloud contextualisation. The code (what a segment asserts) and coverage (how completely the dimension is treated) are separate attributes.</t>
         </is>
       </c>
     </row>
